--- a/output/pdf_financials_xlsx/ABM.xlsx
+++ b/output/pdf_financials_xlsx/ABM.xlsx
@@ -6151,46 +6151,46 @@
         <v>1.86497</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.069359</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.074226</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.074226</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.210403</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.210403</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.284453</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.655074</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.256467</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.662729</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.662729</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.126438</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.330547</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.330547</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.331292</v>
       </c>
     </row>
     <row r="93">
@@ -10450,7 +10450,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -11600,7 +11604,11 @@
           <t>Reserves (Note 8) 4,330,547</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -12748,7 +12756,11 @@
           <t>Reserves (Note 8) 4,187,455</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -13632,7 +13644,11 @@
           <t>Reserves (Note 9) 4,011,113</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -14572,7 +14588,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -15590,7 +15610,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -16280,7 +16304,11 @@
           <t>Reserves (Note 8) 2,210,403</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -17068,7 +17096,11 @@
           <t>Reserves (Note 8) 2,074,226</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -17544,7 +17576,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ABM.xlsx
+++ b/output/pdf_financials_xlsx/ABM.xlsx
@@ -1143,16 +1143,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.011513</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.006875</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.04706</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.024757</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.003448</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.032814</v>
+        <v>-1.044327</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.48415</v>
+        <v>-0.491025</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.784423</v>
+        <v>-2.831483</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.788385</v>
+        <v>-0.813142</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.104296</v>
+        <v>-1.107744</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.487859</v>
@@ -2416,16 +2416,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.032814</v>
+        <v>-1.044327</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.48415</v>
+        <v>-0.491025</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.784423</v>
+        <v>-2.831483</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.788385</v>
+        <v>-0.813142</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.104296</v>
+        <v>-1.107744</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.487859</v>
@@ -2782,13 +2782,13 @@
         <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.119263</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.059081</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="35">
@@ -2892,13 +2892,13 @@
         <v>0.1525</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.119263</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.0135</v>
+        <v>0.07258100000000001</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="37">
@@ -3552,13 +3552,13 @@
         <v>0.788063</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.164091</v>
+        <v>0.044828</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.09384099999999999</v>
+        <v>0.03476</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.033331</v>
+        <v>0.011431</v>
       </c>
     </row>
     <row r="49">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9702,7 +9702,11 @@
           <t>Reclamation deposit (Note 6)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -10912,7 +10916,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -11210,7 +11214,11 @@
           <t>Reclamation deposit (Note 6) 47,000</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -13248,7 +13256,11 @@
           <t>Reclamation deposit (Note 7) 38,000</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -14124,7 +14136,11 @@
           <t>Reclamation deposit (Note 7)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -20344,7 +20360,11 @@
           <t>Refund of reclamation deposit</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -30334,7 +30354,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -31108,7 +31128,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -33340,7 +33360,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E252" s="5" t="n">
